--- a/DataRepo/tests/data/isoautocorr/test-isoautocorr-study/test-isoautocorr-studydoc_v3.xlsx
+++ b/DataRepo/tests/data/isoautocorr/test-isoautocorr-study/test-isoautocorr-studydoc_v3.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11110"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10628"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rleach/PROJECT-local/TRACEBASE/tracebase/DataRepo/data/tests/isoautocorr/test-isoautocorr-study/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rleach/PROJECT-local/TRACEBASE/tracebase/DataRepo/tests/data/isoautocorr/test-isoautocorr-study/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCB396BE-A51A-024C-A8FD-67BD95BEF1C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E505CC16-0BA8-F945-AEBC-6DD07DFA5CA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="12640" windowWidth="32400" windowHeight="9300" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="12640" windowWidth="32400" windowHeight="9300" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Study" sheetId="1" r:id="rId1"/>
@@ -1772,9 +1772,6 @@
     <t>Michael Neinast, polar-HILIC-25-min, Exploris480, 2024-05-23</t>
   </si>
   <si>
-    <t>DataRepo/data/tests/isoautocorr/test-isoautocorr-study/test-isoautocorr-negative-cor.xlsx</t>
-  </si>
-  <si>
     <t>His_M3_T02_liv</t>
   </si>
   <si>
@@ -1818,6 +1815,9 @@
   </si>
   <si>
     <t>his</t>
+  </si>
+  <si>
+    <t>DataRepo/tests/data/isoautocorr/test-isoautocorr-study/test-isoautocorr-negative-cor.xlsx</t>
   </si>
 </sst>
 </file>
@@ -3297,30 +3297,30 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B2" t="s">
         <v>108</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>109</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>110</v>
-      </c>
-      <c r="D2" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
+        <v>111</v>
+      </c>
+      <c r="B3" t="s">
         <v>112</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>113</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>114</v>
-      </c>
-      <c r="D3" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -3328,13 +3328,13 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
+        <v>115</v>
+      </c>
+      <c r="C4" t="s">
         <v>116</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>117</v>
-      </c>
-      <c r="D4" t="s">
-        <v>118</v>
       </c>
     </row>
   </sheetData>
@@ -4246,7 +4246,7 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B2" t="s">
         <v>49</v>
@@ -4266,7 +4266,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B3" t="s">
         <v>49</v>
@@ -4286,7 +4286,7 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B4" t="s">
         <v>49</v>
@@ -4306,7 +4306,7 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B5" t="s">
         <v>49</v>
@@ -4602,7 +4602,7 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>103</v>
+        <v>118</v>
       </c>
       <c r="B2" t="s">
         <v>101</v>
@@ -4684,7 +4684,7 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B2" t="s">
         <v>45</v>
@@ -4698,7 +4698,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B3" t="s">
         <v>46</v>
@@ -4712,7 +4712,7 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B4" t="s">
         <v>48</v>
@@ -4726,7 +4726,7 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B5" t="s">
         <v>47</v>
